--- a/BVSimulationFiles/91.xlsx
+++ b/BVSimulationFiles/91.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0005333333333333334</v>
+        <v>0.001066666666666667</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0005080821951359313</v>
+        <v>0.001016164390271863</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0004838737416374842</v>
+        <v>0.0009677474832749684</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0004606782552677068</v>
+        <v>0.0009213565105354136</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000438465531023349</v>
+        <v>0.000876931062046698</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0004172050618997407</v>
+        <v>0.0008344101237994814</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0003968662024987922</v>
+        <v>0.0007937324049975844</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0003774183128528058</v>
+        <v>0.0007548366257056116</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0003588308843314458</v>
+        <v>0.0007176617686628916</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0003410736493409025</v>
+        <v>0.000682147298681805</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003241166763786114</v>
+        <v>0.0006482333527572228</v>
       </c>
       <c r="M2" t="n">
-        <v>0.000307930451872873</v>
+        <v>0.000615860903745746</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00029248595011348</v>
+        <v>0.00058497190022696</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0002777546924661524</v>
+        <v>0.0005555093849323048</v>
       </c>
       <c r="P2" t="n">
-        <v>0.000263708796959445</v>
+        <v>0.0005274175939188899</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.000250321019237117</v>
+        <v>0.000500642038474234</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0002375647857810768</v>
+        <v>0.0004751295715621536</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0002254142202293362</v>
+        <v>0.0004508284404586724</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0002138441635393581</v>
+        <v>0.0004276883270787162</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0002028301886792453</v>
+        <v>0.0004056603773584906</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0005333333333333334</v>
+        <v>0.001066666666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005080821951359313</v>
+        <v>0.001016164390271863</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0004838737416374842</v>
+        <v>0.0009677474832749684</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004606782552677068</v>
+        <v>0.0009213565105354136</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000438465531023349</v>
+        <v>0.000876931062046698</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0004172050618997407</v>
+        <v>0.0008344101237994814</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0003968662024987922</v>
+        <v>0.0007937324049975844</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0003774183128528058</v>
+        <v>0.0007548366257056116</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003588308843314458</v>
+        <v>0.0007176617686628916</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0003410736493409025</v>
+        <v>0.000682147298681805</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003241166763786114</v>
+        <v>0.0006482333527572228</v>
       </c>
       <c r="M3" t="n">
-        <v>0.000307930451872873</v>
+        <v>0.000615860903745746</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00029248595011348</v>
+        <v>0.00058497190022696</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0002777546924661524</v>
+        <v>0.0005555093849323048</v>
       </c>
       <c r="P3" t="n">
-        <v>0.000263708796959445</v>
+        <v>0.0005274175939188899</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.000250321019237117</v>
+        <v>0.000500642038474234</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0002375647857810768</v>
+        <v>0.0004751295715621536</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0002254142202293362</v>
+        <v>0.0004508284404586724</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0002138441635393581</v>
+        <v>0.0004276883270787162</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0002028301886792453</v>
+        <v>0.0004056603773584906</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/91.xlsx
+++ b/BVSimulationFiles/91.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001066666666666667</v>
+        <v>0.01066666666666667</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001016164390271863</v>
+        <v>0.01016164390271863</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0009677474832749684</v>
+        <v>0.009677474832749684</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0009213565105354136</v>
+        <v>0.009213565105354135</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000876931062046698</v>
+        <v>0.008769310620466981</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008344101237994814</v>
+        <v>0.008344101237994814</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007937324049975844</v>
+        <v>0.007937324049975844</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007548366257056116</v>
+        <v>0.007548366257056116</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007176617686628916</v>
+        <v>0.007176617686628916</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000682147298681805</v>
+        <v>0.00682147298681805</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006482333527572228</v>
+        <v>0.006482333527572227</v>
       </c>
       <c r="M2" t="n">
-        <v>0.000615860903745746</v>
+        <v>0.00615860903745746</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00058497190022696</v>
+        <v>0.0058497190022696</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0005555093849323048</v>
+        <v>0.005555093849323048</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0005274175939188899</v>
+        <v>0.005274175939188899</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.000500642038474234</v>
+        <v>0.005006420384742341</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0004751295715621536</v>
+        <v>0.004751295715621536</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0004508284404586724</v>
+        <v>0.004508284404586724</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0004276883270787162</v>
+        <v>0.004276883270787162</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0004056603773584906</v>
+        <v>0.004056603773584906</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001066666666666667</v>
+        <v>0.01066666666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001016164390271863</v>
+        <v>0.01016164390271863</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009677474832749684</v>
+        <v>0.009677474832749684</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0009213565105354136</v>
+        <v>0.009213565105354135</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000876931062046698</v>
+        <v>0.008769310620466981</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008344101237994814</v>
+        <v>0.008344101237994814</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007937324049975844</v>
+        <v>0.007937324049975844</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007548366257056116</v>
+        <v>0.007548366257056116</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0007176617686628916</v>
+        <v>0.007176617686628916</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000682147298681805</v>
+        <v>0.00682147298681805</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006482333527572228</v>
+        <v>0.006482333527572227</v>
       </c>
       <c r="M3" t="n">
-        <v>0.000615860903745746</v>
+        <v>0.00615860903745746</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00058497190022696</v>
+        <v>0.0058497190022696</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0005555093849323048</v>
+        <v>0.005555093849323048</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0005274175939188899</v>
+        <v>0.005274175939188899</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.000500642038474234</v>
+        <v>0.005006420384742341</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0004751295715621536</v>
+        <v>0.004751295715621536</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0004508284404586724</v>
+        <v>0.004508284404586724</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0004276883270787162</v>
+        <v>0.004276883270787162</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0004056603773584906</v>
+        <v>0.004056603773584906</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/91.xlsx
+++ b/BVSimulationFiles/91.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,61 +421,19 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.03717578947368421</v>
+        <v>0.02435655172413793</v>
       </c>
       <c r="D1" t="n">
-        <v>0.07435157894736842</v>
+        <v>0.04871310344827586</v>
       </c>
       <c r="E1" t="n">
-        <v>0.1115273684210526</v>
+        <v>0.07306965517241379</v>
       </c>
       <c r="F1" t="n">
-        <v>0.1487031578947368</v>
+        <v>0.09742620689655172</v>
       </c>
       <c r="G1" t="n">
-        <v>0.1858789473684211</v>
-      </c>
-      <c r="H1" t="n">
-        <v>0.2230547368421053</v>
-      </c>
-      <c r="I1" t="n">
-        <v>0.2602305263157895</v>
-      </c>
-      <c r="J1" t="n">
-        <v>0.2974063157894737</v>
-      </c>
-      <c r="K1" t="n">
-        <v>0.3345821052631579</v>
-      </c>
-      <c r="L1" t="n">
-        <v>0.3717578947368421</v>
-      </c>
-      <c r="M1" t="n">
-        <v>0.4089336842105263</v>
-      </c>
-      <c r="N1" t="n">
-        <v>0.4461094736842105</v>
-      </c>
-      <c r="O1" t="n">
-        <v>0.4832852631578948</v>
-      </c>
-      <c r="P1" t="n">
-        <v>0.5204610526315789</v>
-      </c>
-      <c r="Q1" t="n">
-        <v>0.5576368421052631</v>
-      </c>
-      <c r="R1" t="n">
-        <v>0.5948126315789474</v>
-      </c>
-      <c r="S1" t="n">
-        <v>0.6319884210526316</v>
-      </c>
-      <c r="T1" t="n">
-        <v>0.6691642105263158</v>
-      </c>
-      <c r="U1" t="n">
-        <v>0.70634</v>
+        <v>0.1217827586206896</v>
       </c>
     </row>
     <row r="2">
@@ -483,64 +441,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01066666666666667</v>
+        <v>0.03502333996877478</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01016164390271863</v>
+        <v>0.03431056362549877</v>
       </c>
       <c r="D2" t="n">
-        <v>0.009677474832749684</v>
+        <v>0.03347320480365573</v>
       </c>
       <c r="E2" t="n">
-        <v>0.009213565105354135</v>
+        <v>0.03253699050228338</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008769310620466981</v>
+        <v>0.03152422392453944</v>
       </c>
       <c r="G2" t="n">
-        <v>0.008344101237994814</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.007937324049975844</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.007548366257056116</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.007176617686628916</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.00682147298681805</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.006482333527572227</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.00615860903745746</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.0058497190022696</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.005555093849323048</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.005274175939188899</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.005006420384742341</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.004751295715621536</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.004508284404586724</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.004276883270787162</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.004056603773584906</v>
+        <v>0.03045417654392799</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +464,22 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01066666666666667</v>
+        <v>0.03502333996877478</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01016164390271863</v>
+        <v>0.03431056362549877</v>
       </c>
       <c r="D3" t="n">
-        <v>0.009677474832749684</v>
+        <v>0.03347320480365573</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009213565105354135</v>
+        <v>0.03253699050228338</v>
       </c>
       <c r="F3" t="n">
-        <v>0.008769310620466981</v>
+        <v>0.03152422392453944</v>
       </c>
       <c r="G3" t="n">
-        <v>0.008344101237994814</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.007937324049975844</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.007548366257056116</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.007176617686628916</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.00682147298681805</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.006482333527572227</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.00615860903745746</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.0058497190022696</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.005555093849323048</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.005274175939188899</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.005006420384742341</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.004751295715621536</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.004508284404586724</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.004276883270787162</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.004056603773584906</v>
+        <v>0.03045417654392799</v>
       </c>
     </row>
   </sheetData>
